--- a/output/pdf_financials_xlsx/HHH.xlsx
+++ b/output/pdf_financials_xlsx/HHH.xlsx
@@ -4780,43 +4780,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.720049</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.769347</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.773287</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.773287</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.773287</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.773287</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.000269</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.99466</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.993532</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.999042</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.993082</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.136239</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.805505</v>
       </c>
     </row>
     <row r="93">
@@ -8017,7 +8017,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -8876,7 +8880,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10972,7 +10980,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -11693,7 +11705,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -12264,7 +12280,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13244,7 +13264,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -14275,7 +14299,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -14830,7 +14858,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>4.720049</v>
       </c>

--- a/output/pdf_financials_xlsx/HHH.xlsx
+++ b/output/pdf_financials_xlsx/HHH.xlsx
@@ -841,19 +841,19 @@
         <v>0.264726</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.190112</v>
+        <v>0.296712</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.177855</v>
+        <v>0.24532</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.266216</v>
+        <v>0.333991</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.197036</v>
+        <v>0.404345</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.5461</v>
+        <v>1.604548</v>
       </c>
     </row>
     <row r="11">
@@ -887,10 +887,10 @@
         <v>-0.264726</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.18498</v>
+        <v>-0.29158</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.177837</v>
+        <v>-0.245302</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-0.333974</v>
@@ -930,16 +930,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005132</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005132</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1692,16 +1692,16 @@
         <v>-0.697755</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.282736</v>
+        <v>-0.287868</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.296712</v>
+        <v>-0.301844</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.245302</v>
+        <v>-0.24532</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.320954</v>
+        <v>-0.320971</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.443084</v>
@@ -1784,16 +1784,16 @@
         <v>-0.697755</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.282736</v>
+        <v>-0.287868</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.296712</v>
+        <v>-0.301844</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.245302</v>
+        <v>-0.24532</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.320954</v>
+        <v>-0.320971</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.443084</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-5781.605611847233</v>
+        <v>-5881.605611847233</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1362788.888888889</v>
+        <v>-1362888.888888889</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1887964.705882353</v>
+        <v>-1888064.705882353</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -1994,43 +1994,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018558</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.043966</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.116423</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.036272</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000669</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.04247</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.018983</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.137687</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.017107</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.260879</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.023062</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.553474</v>
       </c>
     </row>
     <row r="35">
@@ -2086,43 +2086,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018558</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.043966</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.116423</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.036272</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000669</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.04247</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.018983</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.137687</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.017107</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.260879</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.023062</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.553474</v>
       </c>
     </row>
     <row r="37">
@@ -2638,43 +2638,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.030245</v>
+        <v>0.011687</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.143243</v>
+        <v>0.099277</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.156092</v>
+        <v>0.039669</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.068532</v>
+        <v>0.03226</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.028094</v>
+        <v>0.027425</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.072505</v>
+        <v>0.030035</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.07996300000000001</v>
+        <v>0.06098</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.15518</v>
+        <v>0.017493</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.081538</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.017331</v>
+        <v>0.000224</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.264113</v>
+        <v>0.003234</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.023999</v>
+        <v>0.000937</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.964309</v>
+        <v>0.410835</v>
       </c>
     </row>
     <row r="49">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -19539,7 +19539,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -20669,7 +20673,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -33086,7 +33094,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -33809,7 +33817,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -34868,7 +34876,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -36563,7 +36571,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -37069,7 +37077,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -37571,7 +37579,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -38845,7 +38853,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">

--- a/output/pdf_financials_xlsx/HHH.xlsx
+++ b/output/pdf_financials_xlsx/HHH.xlsx
@@ -679,43 +679,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.240323</v>
+        <v>0.243151</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.170714</v>
+        <v>0.174899</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.150756</v>
+        <v>0.152688</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.059169</v>
+        <v>0.060525</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.060593</v>
+        <v>0.066652</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.062541</v>
+        <v>0.067663</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.317039</v>
+        <v>0.342222</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.199309</v>
+        <v>0.204918</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.190112</v>
+        <v>0.229585</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.177855</v>
+        <v>0.190264</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.266216</v>
+        <v>0.277033</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.197036</v>
+        <v>0.2023</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.5461</v>
+        <v>0.563358</v>
       </c>
     </row>
     <row r="8">
@@ -3458,13 +3458,13 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.177922</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.134803</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.349952</v>
       </c>
     </row>
     <row r="65">
@@ -3590,19 +3590,19 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.050048</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.045187</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.037522</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.045667</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.088987</v>
       </c>
     </row>
     <row r="68">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000781</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000781</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.352812</v>
+        <v>-0.353593</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.371337</v>
@@ -31736,7 +31736,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E311" s="5" t="n">
         <v>-0.000781</v>
       </c>
@@ -32696,7 +32700,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E323" s="5" t="n">
         <v>0.002828</v>
       </c>
@@ -37160,7 +37168,11 @@
           <t>Office expenses 39,473</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
